--- a/ForHome8/DataScience/data_audit_task03.xlsx
+++ b/ForHome8/DataScience/data_audit_task03.xlsx
@@ -220,9 +220,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>252720</xdr:colOff>
+      <xdr:colOff>252360</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>37080</xdr:rowOff>
+      <xdr:rowOff>36720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -236,7 +236,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1390320"/>
-          <a:ext cx="5094720" cy="3980880"/>
+          <a:ext cx="5094720" cy="3980520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -257,9 +257,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>762840</xdr:colOff>
+      <xdr:colOff>762480</xdr:colOff>
       <xdr:row>104</xdr:row>
-      <xdr:rowOff>46800</xdr:rowOff>
+      <xdr:rowOff>46440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -273,7 +273,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="5800320"/>
-          <a:ext cx="14067360" cy="14058360"/>
+          <a:ext cx="14076360" cy="14058000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -299,9 +299,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273600</xdr:colOff>
+      <xdr:colOff>273240</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -314,8 +314,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838160" y="0"/>
-          <a:ext cx="7626960" cy="5714280"/>
+          <a:off x="1840320" y="0"/>
+          <a:ext cx="7634160" cy="5713920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -341,9 +341,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273600</xdr:colOff>
+      <xdr:colOff>273240</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -356,8 +356,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838160" y="0"/>
-          <a:ext cx="7626960" cy="5714280"/>
+          <a:off x="1840320" y="0"/>
+          <a:ext cx="7634160" cy="5713920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -383,9 +383,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273600</xdr:colOff>
+      <xdr:colOff>273240</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -398,8 +398,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838160" y="0"/>
-          <a:ext cx="7626960" cy="5714280"/>
+          <a:off x="1840320" y="0"/>
+          <a:ext cx="7634160" cy="5713920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -425,9 +425,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273600</xdr:colOff>
+      <xdr:colOff>273240</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -440,8 +440,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838160" y="0"/>
-          <a:ext cx="7626960" cy="5714280"/>
+          <a:off x="1840320" y="0"/>
+          <a:ext cx="7634160" cy="5713920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -467,9 +467,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273600</xdr:colOff>
+      <xdr:colOff>273240</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -482,8 +482,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838160" y="0"/>
-          <a:ext cx="7626960" cy="5714280"/>
+          <a:off x="1840320" y="0"/>
+          <a:ext cx="7634160" cy="5713920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -509,9 +509,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273600</xdr:colOff>
+      <xdr:colOff>273240</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -524,8 +524,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838160" y="0"/>
-          <a:ext cx="7626960" cy="5714280"/>
+          <a:off x="1840320" y="0"/>
+          <a:ext cx="7634160" cy="5713920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -551,9 +551,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273600</xdr:colOff>
+      <xdr:colOff>273240</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -566,8 +566,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838160" y="0"/>
-          <a:ext cx="7626960" cy="5714280"/>
+          <a:off x="1840320" y="0"/>
+          <a:ext cx="7634160" cy="5713920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -588,9 +588,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.46"/>
@@ -909,7 +909,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B67"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1465,7 +1465,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B73"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2069,7 +2069,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B63"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2593,7 +2593,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B73"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3197,7 +3197,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B70"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3777,7 +3777,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -4165,7 +4165,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
